--- a/banco_ops.xlsx
+++ b/banco_ops.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -696,6 +696,612 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5219</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CETOR DUO</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>934</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>PERFIL: CANTONEIRA DE ABAS IGUAIS - A 25,4 - E 1,58 MM / 1' X 1/16 Nível Otimização: 1 (7° ETAPA - ESTRUTURA VF39.AP3201)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>143 mm (90/90º)</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>14</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>14</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>CT016</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>5219</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CETOR DUO</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>934</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>PERFIL: CANTONEIRA DE ABAS IGUAIS - A 25,4 - E 1,58 MM / 1' X 1/16 Nível Otimização: 1 (7° ETAPA - ESTRUTURA VF39.AP3201)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>94 mm (90/90º)</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>14</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>14</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>CT016</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>5219</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CETOR DUO</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>934</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>PERFIL: CANTONEIRA DE ABAS IGUAIS - A 25,4 - E 1,58 MM / 1' X 1/16 Nível Otimização: 1 (7° ETAPA - ESTRUTURA VF39.AP3201)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1220 mm (45/45º)</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>CT016</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>5219</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CETOR DUO</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>934</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>PERFIL: CANTONEIRA DE ABAS IGUAIS - A 25,4 - E 1,58 MM / 1' X 1/16 Nível Otimização: 1 (7° ETAPA - ESTRUTURA VF39.AP3201)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1020 mm (45/45º)</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>CT016</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>5219</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CETOR DUO</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>934</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PERFIL: CANTONEIRA DE ABAS IGUAIS - A 25,4 - E 1,58 MM / 1' X 1/16 Nível Otimização: 1 (7° ETAPA - ESTRUTURA VF39.AP3201)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1125 mm (45/45º)</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>CT016</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>5219</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CETOR DUO</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>934</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PERFIL: CANTONEIRA DE ABAS IGUAIS - A 25,4 - E 1,58 MM / 1' X 1/16 Nível Otimização: 1 (7° ETAPA - ESTRUTURA VF39.AP3201)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1020 mm (45/45º)</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>6</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>CT016</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>5219</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CETOR DUO</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>934</v>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>PERFIL: TUBO RETANGULAR - A 101,6 X B 50,8 - E 2,00 MM Nível Otimização: 1 (7° ETAPA - ESTRUTURA VF39.AP3201)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>6016 mm (90/90º)</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>TG072</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5219</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CETOR DUO</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>934</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>PERFIL: TUBO RETANGULAR - A 101,6 X B 50,8 - E 2,00 MM Nível Otimização: 1 (7° ETAPA - ESTRUTURA VF39.AP3201)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2841 mm (90/90º)</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>TG072</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>5219</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CETOR DUO</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>934</v>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PERFIL: TUBO RETANGULAR - A 101,6 X B 50,8 - E 2,00 MM Nível Otimização: 1 (7° ETAPA - ESTRUTURA VF39.AP3201)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1025 mm (90/90º)</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>TG072</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>5219</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CETOR DUO</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>934</v>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>PERFIL: TUBO RETANGULAR - A 152,4 X B 50,8 - E 3 MM Nível Otimização: 1 (7° ETAPA - ESTRUTURA VF39.AP3201)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>6016 mm (90/90º)</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>TG082</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>5219</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CETOR DUO</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>934</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PERFIL: TUBO RETANGULAR - A 152,4 X B 50,8 - E 3 MM Nível Otimização: 1 (7° ETAPA - ESTRUTURA VF39.AP3201)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2841 mm (90/90º)</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>TG082</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>5219</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CETOR DUO</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>934</v>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>PERFIL: TUBO RETANGULAR - A 152,4 X B 50,8 - E 3 MM Nível Otimização: 1 (7° ETAPA - ESTRUTURA VF39.AP3201)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1025 mm (90/90º)</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>TG082</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>5222</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PLANETAPEIA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PORTA DE CORRER - 3 FOLHAS - GOLD IV - HYDRO (PORTAS DE CORRER)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>3665 x 2375 mm</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>5222</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PLANETAPEIA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>PORTA DE CORRER - 3 FOLHAS - GOLD IV - HYDRO (PORTAS DE CORRER)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>3665 x 2400 mm</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>5222</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PLANETAPEIA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PORTA DE CORRER - 3 FOLHAS - GOLD IV - HYDRO (PORTAS DE CORRER)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>3665 x 2400 mm</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_ops.xlsx
+++ b/banco_ops.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,78 +469,84 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1100 - duo - janelas desenfumagem - listas de itens</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>J01</t>
-        </is>
-      </c>
+      <c r="A2" t="n">
+        <v>5215</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CETOR DUO</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>931</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JANELAS DESENFUMAGEM - TORRE 1</t>
+          <t>PORTAS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>772 x 571</t>
+          <t>1120x2783</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>DCSL-VF9-P</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1100 - duo - janelas desenfumagem - listas de itens</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>J01</t>
-        </is>
-      </c>
+      <c r="A3" t="n">
+        <v>5215</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CETOR DUO</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>931</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JANELAS DESENFUMAGEM - TORRE 1</t>
+          <t>PORTAS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>772 x 571</t>
+          <t>1120x2793</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>30</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>DCSL-VF8-P</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>5210</t>
-        </is>
+      <c r="A4" t="n">
+        <v>5215</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -553,34 +559,32 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JANELAS DEFUMAGEM</t>
+          <t>PORTAS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>772x571</t>
+          <t>1114x2794</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>J01</t>
+          <t>DCSL-VF11-P</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>5215</t>
-        </is>
+      <c r="A5" t="n">
+        <v>5219</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -588,39 +592,37 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PORTAS</t>
+          <t>PERFIL: CANTONEIRA DE ABAS IGUAIS - A 25,4 - E 1,58 MM / 1' X 1/16 Nível Otimização: 1 (7° ETAPA - ESTRUTURA VF39.AP3201)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1120x2783</t>
+          <t>143 mm (90/90º)</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>DCSL-VF9-P</t>
+          <t>CT016</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>5215</t>
-        </is>
+      <c r="A6" t="n">
+        <v>5219</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -628,39 +630,37 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PORTAS</t>
+          <t>PERFIL: CANTONEIRA DE ABAS IGUAIS - A 25,4 - E 1,58 MM / 1' X 1/16 Nível Otimização: 1 (7° ETAPA - ESTRUTURA VF39.AP3201)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1120x2793</t>
+          <t>94 mm (90/90º)</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>DCSL-VF8-P</t>
+          <t>CT016</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>5215</t>
-        </is>
+      <c r="A7" t="n">
+        <v>5219</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -668,39 +668,37 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PORTAS</t>
+          <t>PERFIL: CANTONEIRA DE ABAS IGUAIS - A 25,4 - E 1,58 MM / 1' X 1/16 Nível Otimização: 1 (7° ETAPA - ESTRUTURA VF39.AP3201)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1114x2794</t>
+          <t>1220 mm (45/45º)</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>DCSL-VF11-P</t>
+          <t>CT016</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>5219</t>
-        </is>
+      <c r="A8" t="n">
+        <v>5219</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -718,17 +716,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>143 mm (90/90º)</t>
+          <t>1020 mm (45/45º)</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -737,10 +735,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>5219</t>
-        </is>
+      <c r="A9" t="n">
+        <v>5219</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -758,17 +754,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>94 mm (90/90º)</t>
+          <t>1125 mm (45/45º)</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -777,10 +773,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>5219</t>
-        </is>
+      <c r="A10" t="n">
+        <v>5219</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -798,17 +792,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1220 mm (45/45º)</t>
+          <t>1020 mm (45/45º)</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -817,10 +811,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>5219</t>
-        </is>
+      <c r="A11" t="n">
+        <v>5219</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -833,34 +825,32 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PERFIL: CANTONEIRA DE ABAS IGUAIS - A 25,4 - E 1,58 MM / 1' X 1/16 Nível Otimização: 1 (7° ETAPA - ESTRUTURA VF39.AP3201)</t>
+          <t>PERFIL: TUBO RETANGULAR - A 101,6 X B 50,8 - E 2,00 MM Nível Otimização: 1 (7° ETAPA - ESTRUTURA VF39.AP3201)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1020 mm (45/45º)</t>
+          <t>6016 mm (90/90º)</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>CT016</t>
+          <t>TG072</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>5219</t>
-        </is>
+      <c r="A12" t="n">
+        <v>5219</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -873,34 +863,32 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PERFIL: CANTONEIRA DE ABAS IGUAIS - A 25,4 - E 1,58 MM / 1' X 1/16 Nível Otimização: 1 (7° ETAPA - ESTRUTURA VF39.AP3201)</t>
+          <t>PERFIL: TUBO RETANGULAR - A 101,6 X B 50,8 - E 2,00 MM Nível Otimização: 1 (7° ETAPA - ESTRUTURA VF39.AP3201)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1125 mm (45/45º)</t>
+          <t>2841 mm (90/90º)</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>CT016</t>
+          <t>TG072</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>5219</t>
-        </is>
+      <c r="A13" t="n">
+        <v>5219</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -913,34 +901,32 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PERFIL: CANTONEIRA DE ABAS IGUAIS - A 25,4 - E 1,58 MM / 1' X 1/16 Nível Otimização: 1 (7° ETAPA - ESTRUTURA VF39.AP3201)</t>
+          <t>PERFIL: TUBO RETANGULAR - A 101,6 X B 50,8 - E 2,00 MM Nível Otimização: 1 (7° ETAPA - ESTRUTURA VF39.AP3201)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1020 mm (45/45º)</t>
+          <t>1025 mm (90/90º)</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>CT016</t>
+          <t>TG072</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>5219</t>
-        </is>
+      <c r="A14" t="n">
+        <v>5219</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -953,7 +939,7 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PERFIL: TUBO RETANGULAR - A 101,6 X B 50,8 - E 2,00 MM Nível Otimização: 1 (7° ETAPA - ESTRUTURA VF39.AP3201)</t>
+          <t>PERFIL: TUBO RETANGULAR - A 152,4 X B 50,8 - E 3 MM Nível Otimização: 1 (7° ETAPA - ESTRUTURA VF39.AP3201)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -972,15 +958,13 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>TG072</t>
+          <t>TG082</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>5219</t>
-        </is>
+      <c r="A15" t="n">
+        <v>5219</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -993,7 +977,7 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PERFIL: TUBO RETANGULAR - A 101,6 X B 50,8 - E 2,00 MM Nível Otimização: 1 (7° ETAPA - ESTRUTURA VF39.AP3201)</t>
+          <t>PERFIL: TUBO RETANGULAR - A 152,4 X B 50,8 - E 3 MM Nível Otimização: 1 (7° ETAPA - ESTRUTURA VF39.AP3201)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1002,25 +986,23 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>TG072</t>
+          <t>TG082</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>5219</t>
-        </is>
+      <c r="A16" t="n">
+        <v>5219</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1033,7 +1015,7 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PERFIL: TUBO RETANGULAR - A 101,6 X B 50,8 - E 2,00 MM Nível Otimização: 1 (7° ETAPA - ESTRUTURA VF39.AP3201)</t>
+          <t>PERFIL: TUBO RETANGULAR - A 152,4 X B 50,8 - E 3 MM Nível Otimização: 1 (7° ETAPA - ESTRUTURA VF39.AP3201)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1052,251 +1034,119 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>TG072</t>
+          <t>TG082</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>5219</t>
-        </is>
+      <c r="A17" t="n">
+        <v>5222</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CETOR DUO</t>
+          <t>PLANETAPEIA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>934</v>
+        <v>1101</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PERFIL: TUBO RETANGULAR - A 152,4 X B 50,8 - E 3 MM Nível Otimização: 1 (7° ETAPA - ESTRUTURA VF39.AP3201)</t>
+          <t>PORTA DE CORRER - 3 FOLHAS - GOLD IV - HYDRO (PORTAS DE CORRER)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>6016 mm (90/90º)</t>
+          <t>3665 x 2375 mm</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>TG082</t>
+          <t>P01</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>5219</t>
-        </is>
+      <c r="A18" t="n">
+        <v>5222</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CETOR DUO</t>
+          <t>PLANETAPEIA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>934</v>
+        <v>1101</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PERFIL: TUBO RETANGULAR - A 152,4 X B 50,8 - E 3 MM Nível Otimização: 1 (7° ETAPA - ESTRUTURA VF39.AP3201)</t>
+          <t>PORTA DE CORRER - 3 FOLHAS - GOLD IV - HYDRO (PORTAS DE CORRER)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2841 mm (90/90º)</t>
+          <t>3665 x 2400 mm</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>TG082</t>
+          <t>P02</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>5219</t>
-        </is>
+      <c r="A19" t="n">
+        <v>5222</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CETOR DUO</t>
+          <t>PLANETAPEIA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>934</v>
+        <v>1101</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PERFIL: TUBO RETANGULAR - A 152,4 X B 50,8 - E 3 MM Nível Otimização: 1 (7° ETAPA - ESTRUTURA VF39.AP3201)</t>
+          <t>PORTA DE CORRER - 3 FOLHAS - GOLD IV - HYDRO (PORTAS DE CORRER)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1025 mm (90/90º)</t>
+          <t>3665 x 2400 mm</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J19" t="inlineStr">
-        <is>
-          <t>TG082</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>5222</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>PLANETAPEIA</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>PORTA DE CORRER - 3 FOLHAS - GOLD IV - HYDRO (PORTAS DE CORRER)</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>3665 x 2375 mm</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>P01</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>5222</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>PLANETAPEIA</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>PORTA DE CORRER - 3 FOLHAS - GOLD IV - HYDRO (PORTAS DE CORRER)</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>3665 x 2400 mm</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>P02</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>5222</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>PLANETAPEIA</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>PORTA DE CORRER - 3 FOLHAS - GOLD IV - HYDRO (PORTAS DE CORRER)</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>3665 x 2400 mm</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" t="inlineStr">
         <is>
           <t>P03</t>
         </is>
